--- a/Multi-site_OSPF-network/addressing/full-addressing.xlsx
+++ b/Multi-site_OSPF-network/addressing/full-addressing.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\ME\COURSES&amp;SCRIPTS\Money\Career\Labs\Networking\Networking-labs\Multi-site_OSPF-network\addressing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\ME\COURSES&amp;SCRIPTS\Personal\Labs\Network\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2AC7C38-3FC1-457E-973C-3AA549F2E876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2593E41A-FA15-4B89-B5FF-4B262136B126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="456" windowWidth="23256" windowHeight="12612" xr2:uid="{33750CF5-BBD9-4B5B-8D85-6CA0B908E1FA}"/>
+    <workbookView xWindow="-108" yWindow="456" windowWidth="23256" windowHeight="12612" xr2:uid="{5231CA2F-D287-4267-B144-8E0B9B906376}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Devices" sheetId="1" r:id="rId1"/>
+    <sheet name="VLANs" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -38,29 +37,511 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="121">
+  <si>
+    <t>Interfaces</t>
+  </si>
+  <si>
+    <t>ip address</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Router-E1</t>
+  </si>
+  <si>
+    <t>Router-E2</t>
+  </si>
+  <si>
+    <t>Equipments &amp; model</t>
+  </si>
+  <si>
+    <t>Router 1841</t>
+  </si>
+  <si>
+    <t>fastethernet 0/0</t>
+  </si>
+  <si>
+    <t>serial 0/0/0</t>
+  </si>
+  <si>
+    <t>fastethernet 0/1</t>
+  </si>
+  <si>
+    <t>192.168.1.253</t>
+  </si>
+  <si>
+    <t>192.168.1.252</t>
+  </si>
+  <si>
+    <t>203.0.113.1</t>
+  </si>
+  <si>
+    <t>203.0.114.1</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>10.0.0.8/30</t>
+  </si>
+  <si>
+    <t>10.0.0.9</t>
+  </si>
+  <si>
+    <t>10.0.0.14</t>
+  </si>
+  <si>
+    <t>10.0.0.12/30</t>
+  </si>
+  <si>
+    <t>192.168.1.0/24</t>
+  </si>
+  <si>
+    <t>203.0.113.0/24</t>
+  </si>
+  <si>
+    <t>TO THE INTERN NETWORK</t>
+  </si>
+  <si>
+    <t>TO THE DMZ SWITCH</t>
+  </si>
+  <si>
+    <t>TO THE INTERNET</t>
+  </si>
+  <si>
+    <t>10.0.0.10</t>
+  </si>
+  <si>
+    <t>serial 0/0/1</t>
+  </si>
+  <si>
+    <t>203.0.113.2</t>
+  </si>
+  <si>
+    <t>203.0.114.2</t>
+  </si>
+  <si>
+    <t>Hostname</t>
+  </si>
+  <si>
+    <t>SW-C1</t>
+  </si>
+  <si>
+    <t>gigabitethernet 1/0/1</t>
+  </si>
+  <si>
+    <t>gigabitethernet 1/0/3</t>
+  </si>
+  <si>
+    <t>gigabitethernet 1/0/2</t>
+  </si>
+  <si>
+    <t>gigabitethernet 1/0/4-6</t>
+  </si>
+  <si>
+    <t>SW-C2</t>
+  </si>
+  <si>
+    <t>10.0.0.0/30</t>
+  </si>
+  <si>
+    <t>10.0.0.4/30</t>
+  </si>
+  <si>
+    <t>10.0.0.20/30</t>
+  </si>
+  <si>
+    <t>10.0.0.16/30</t>
+  </si>
+  <si>
+    <t>10.0.0.2</t>
+  </si>
+  <si>
+    <t>10.0.0.5</t>
+  </si>
+  <si>
+    <t>10.0.0.22</t>
+  </si>
+  <si>
+    <t>10.0.0.13</t>
+  </si>
+  <si>
+    <t>10.0.0.18</t>
+  </si>
+  <si>
+    <t>10.0.0.21</t>
+  </si>
+  <si>
+    <t>TO SW-D1</t>
+  </si>
+  <si>
+    <t>TO SW-D2</t>
+  </si>
+  <si>
+    <t>TO SW-AD1</t>
+  </si>
+  <si>
+    <t>TO ROUTER-E2</t>
+  </si>
+  <si>
+    <t>TO ROUTER-E1</t>
+  </si>
+  <si>
+    <t>PORTCHANNEL 1 TO SW-C2</t>
+  </si>
+  <si>
+    <t>PORTCHANNEL 1 TO SW-C1</t>
+  </si>
+  <si>
+    <t>Multilayer Switch 3650-24APS</t>
+  </si>
+  <si>
+    <t>Switch 2950-24</t>
+  </si>
+  <si>
+    <t>SW-A1</t>
+  </si>
+  <si>
+    <t>fastethernet 0/21</t>
+  </si>
+  <si>
+    <t>fastethernet 0/22</t>
+  </si>
+  <si>
+    <t>TO SW-C1</t>
+  </si>
+  <si>
+    <t>TO SW-C2</t>
+  </si>
+  <si>
+    <t>SW-A2</t>
+  </si>
+  <si>
+    <t>SW-AD1</t>
+  </si>
+  <si>
+    <t>gigabitethernet 1/0/24</t>
+  </si>
+  <si>
+    <t>10.0.0.17</t>
+  </si>
+  <si>
+    <t>gigabitethernet 1/0/23</t>
+  </si>
+  <si>
+    <t>TO DHCP SERVER</t>
+  </si>
+  <si>
+    <t>172.16.1.0/24</t>
+  </si>
+  <si>
+    <t>172.16.1.1</t>
+  </si>
+  <si>
+    <t>SW-A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gigabitethernet 1/0/1-4 </t>
+  </si>
+  <si>
+    <t>VLAN 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gigabitethernet 1/0/5-8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fastethernet 0/1-10 </t>
+  </si>
+  <si>
+    <t>VLAN 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fastethernet 0/11-20 </t>
+  </si>
+  <si>
+    <t>VLAN 20</t>
+  </si>
+  <si>
+    <t>VLAN 30</t>
+  </si>
+  <si>
+    <t>VLAN 40</t>
+  </si>
+  <si>
+    <t>VLAN 60</t>
+  </si>
+  <si>
+    <t>172.16.0.129</t>
+  </si>
+  <si>
+    <t>172.16.0.161</t>
+  </si>
+  <si>
+    <t>172.16.0.128/27</t>
+  </si>
+  <si>
+    <t>172.16.0.160/27</t>
+  </si>
+  <si>
+    <t>172.16.0.0/27</t>
+  </si>
+  <si>
+    <t>172.16.0.32/27</t>
+  </si>
+  <si>
+    <t>172.16.0.64/27</t>
+  </si>
+  <si>
+    <t>172.16.0.96/27</t>
+  </si>
+  <si>
+    <t>TRUNK</t>
+  </si>
+  <si>
+    <t>SW-D1</t>
+  </si>
+  <si>
+    <t>gigabitethernet 1/0/4</t>
+  </si>
+  <si>
+    <t>TO SW-A1</t>
+  </si>
+  <si>
+    <t>TO SW-A3</t>
+  </si>
+  <si>
+    <t>TO SW-A2</t>
+  </si>
+  <si>
+    <t>10.0.0.1</t>
+  </si>
+  <si>
+    <t>SW-D2</t>
+  </si>
+  <si>
+    <t>10.0.0.6</t>
+  </si>
+  <si>
+    <t>VLANs</t>
+  </si>
+  <si>
+    <t>Gateway equipment</t>
+  </si>
+  <si>
+    <t>172.16.0.32/30</t>
+  </si>
+  <si>
+    <t>172.16.0.97</t>
+  </si>
+  <si>
+    <t>172.16.0.98</t>
+  </si>
+  <si>
+    <t>Comptability</t>
+  </si>
+  <si>
+    <t>Financy</t>
+  </si>
+  <si>
+    <t>ServiceClient</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>SecurityDepartment</t>
+  </si>
+  <si>
+    <t>ResearchDepartment</t>
+  </si>
+  <si>
+    <t>Primary gateway ip | secondary</t>
+  </si>
+  <si>
+    <t>172.16.0.1 | 172.16.0.2</t>
+  </si>
+  <si>
+    <t>172.16.0.33 | 172.16.0.34</t>
+  </si>
+  <si>
+    <t>172.16.0.65 | 172.16.0.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.16.0.129 </t>
+  </si>
+  <si>
+    <t>SW-D2 | SW-D1</t>
+  </si>
+  <si>
+    <t>SW-D1 | SW-D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW-D2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW-D1 </t>
+  </si>
+  <si>
+    <t>ISPRouter</t>
+  </si>
+  <si>
+    <t>192.168.0.254</t>
+  </si>
+  <si>
+    <t>203.0.114.0/24</t>
+  </si>
+  <si>
+    <t>192.168.0.0/24</t>
+  </si>
+  <si>
+    <t>TO THE SIMULATED INTERNET NETWORK</t>
+  </si>
+  <si>
+    <t>TO Router-E2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -69,8 +550,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -89,9 +613,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -99,39 +623,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -183,7 +707,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -235,7 +759,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -294,6 +818,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -302,13 +833,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -373,41 +897,836 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15522D78-A484-4AEA-8B1C-86BF613B04CD}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67C510D-5DC6-45DA-BDD6-B5CB429F36D6}">
+  <dimension ref="B4:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" customWidth="1"/>
+    <col min="5" max="6" width="28.33203125" customWidth="1"/>
+    <col min="7" max="7" width="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="7"/>
+      <c r="F40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="C36:C39"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="B32:B35"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1213C066-B76F-4AD5-9505-72CEEA2067E5}">
+  <dimension ref="B4:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
+    <col min="6" max="6" width="23.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="10">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="10">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="10">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="20">
+        <v>40</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="10">
+        <v>50</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="10">
+        <v>60</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>